--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J318"/>
+  <dimension ref="A1:J319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11892,6 +11892,42 @@
       <c r="J318" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="C319" t="n">
+        <v>389.82</v>
+      </c>
+      <c r="D319" t="n">
+        <v>390.3</v>
+      </c>
+      <c r="E319" t="n">
+        <v>395.78</v>
+      </c>
+      <c r="F319" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="G319" t="n">
+        <v>399.02</v>
+      </c>
+      <c r="H319" t="n">
+        <v>399.91</v>
+      </c>
+      <c r="I319" t="n">
+        <v>394.43</v>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11906,7 +11942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B327"/>
+  <dimension ref="A1:B328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15179,6 +15215,16 @@
       </c>
       <c r="B327" t="n">
         <v>-0.39</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -15347,28 +15393,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06574508186346807</v>
+        <v>0.06241014907093464</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01375385490228176</v>
+        <v>0.0124434827179104</v>
       </c>
       <c r="M2" t="n">
-        <v>3.106287566210763</v>
+        <v>3.111189615797007</v>
       </c>
       <c r="N2" t="n">
-        <v>16.18753419393552</v>
+        <v>16.21440840115396</v>
       </c>
       <c r="O2" t="n">
-        <v>4.023373484271069</v>
+        <v>4.026711859713078</v>
       </c>
       <c r="P2" t="n">
-        <v>376.911273153665</v>
+        <v>376.9458075713582</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15429,28 +15475,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08580454619430757</v>
+        <v>0.08316954179969679</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02496046672336771</v>
+        <v>0.02358373839353223</v>
       </c>
       <c r="M3" t="n">
-        <v>3.069116068377755</v>
+        <v>3.073606677604394</v>
       </c>
       <c r="N3" t="n">
-        <v>15.02046570149638</v>
+        <v>15.02178805062919</v>
       </c>
       <c r="O3" t="n">
-        <v>3.875624556313005</v>
+        <v>3.875795150756705</v>
       </c>
       <c r="P3" t="n">
-        <v>391.5182660677988</v>
+        <v>391.5455524774653</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15511,28 +15557,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1180897411941054</v>
+        <v>0.1152117437126586</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K4" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05201307066557626</v>
+        <v>0.04977965579571664</v>
       </c>
       <c r="M4" t="n">
-        <v>2.974595919123076</v>
+        <v>2.977645253855155</v>
       </c>
       <c r="N4" t="n">
-        <v>13.27417304294984</v>
+        <v>13.29035531037962</v>
       </c>
       <c r="O4" t="n">
-        <v>3.643373854403339</v>
+        <v>3.645593958517544</v>
       </c>
       <c r="P4" t="n">
-        <v>391.5234953503175</v>
+        <v>391.5532980400049</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15593,28 +15639,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05509877324799085</v>
+        <v>0.05251955485940223</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01370820572242815</v>
+        <v>0.01251230360575062</v>
       </c>
       <c r="M5" t="n">
-        <v>2.657507629910853</v>
+        <v>2.662219756186806</v>
       </c>
       <c r="N5" t="n">
-        <v>11.4078011723412</v>
+        <v>11.41844987341426</v>
       </c>
       <c r="O5" t="n">
-        <v>3.377543659575876</v>
+        <v>3.379119689122339</v>
       </c>
       <c r="P5" t="n">
-        <v>398.2067698417395</v>
+        <v>398.2334785674304</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -15675,28 +15721,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1099903742657812</v>
+        <v>0.1054601381226312</v>
       </c>
       <c r="J6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03919062303399901</v>
+        <v>0.03608111649702317</v>
       </c>
       <c r="M6" t="n">
-        <v>2.878964796487025</v>
+        <v>2.893737741128188</v>
       </c>
       <c r="N6" t="n">
-        <v>15.49022415431695</v>
+        <v>15.5850374185011</v>
       </c>
       <c r="O6" t="n">
-        <v>3.935762207542136</v>
+        <v>3.947788927805171</v>
       </c>
       <c r="P6" t="n">
-        <v>397.4560508000536</v>
+        <v>397.5029630099688</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -15757,28 +15803,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05551494611829266</v>
+        <v>0.0507698241966479</v>
       </c>
       <c r="J7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.013742307016674</v>
+        <v>0.01145001806089352</v>
       </c>
       <c r="M7" t="n">
-        <v>2.597050241437666</v>
+        <v>2.61056982713424</v>
       </c>
       <c r="N7" t="n">
-        <v>11.55164621945565</v>
+        <v>11.67278367886414</v>
       </c>
       <c r="O7" t="n">
-        <v>3.398771280838952</v>
+        <v>3.416545576875002</v>
       </c>
       <c r="P7" t="n">
-        <v>404.6819014619978</v>
+        <v>404.7310388907383</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15839,28 +15885,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1072110993124226</v>
+        <v>0.1007066151150208</v>
       </c>
       <c r="J8" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K8" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06542316064550291</v>
+        <v>0.05673543692669092</v>
       </c>
       <c r="M8" t="n">
-        <v>2.279522956076408</v>
+        <v>2.30358282302968</v>
       </c>
       <c r="N8" t="n">
-        <v>8.57543715621445</v>
+        <v>8.844346941715338</v>
       </c>
       <c r="O8" t="n">
-        <v>2.928384735005708</v>
+        <v>2.973944676976244</v>
       </c>
       <c r="P8" t="n">
-        <v>406.8493632974597</v>
+        <v>406.9167195496321</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15921,28 +15967,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005192381952387838</v>
+        <v>0.0008677973353375327</v>
       </c>
       <c r="J9" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K9" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001562169828474014</v>
+        <v>4.333769389908149e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>2.403467347821742</v>
+        <v>2.417599547902963</v>
       </c>
       <c r="N9" t="n">
-        <v>9.012192214272481</v>
+        <v>9.114641718158529</v>
       </c>
       <c r="O9" t="n">
-        <v>3.002031347982975</v>
+        <v>3.019046491553008</v>
       </c>
       <c r="P9" t="n">
-        <v>400.7811930471516</v>
+        <v>400.8259756622164</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -15984,7 +16030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J318"/>
+  <dimension ref="A1:J319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32523,6 +32569,58 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-35.43434493213486,174.3620254202338</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-35.43498419945772,174.36229778524168</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-35.43557540543505,174.36271476796173</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-35.436144021933856,174.363206682016</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-35.43665571136974,174.36376829693282</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-35.43706507737223,174.36443666467508</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-35.43736583548492,174.3651291922849</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-35.437530961119755,174.3659371604927</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J319"/>
+  <dimension ref="A1:J320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11926,6 +11926,42 @@
         <v>394.43</v>
       </c>
       <c r="J319" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="C320" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="D320" t="n">
+        <v>390.93</v>
+      </c>
+      <c r="E320" t="n">
+        <v>395.83</v>
+      </c>
+      <c r="F320" t="n">
+        <v>394</v>
+      </c>
+      <c r="G320" t="n">
+        <v>399.22</v>
+      </c>
+      <c r="H320" t="n">
+        <v>400.77</v>
+      </c>
+      <c r="I320" t="n">
+        <v>395.32</v>
+      </c>
+      <c r="J320" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11942,7 +11978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15225,6 +15261,16 @@
       </c>
       <c r="B328" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -15393,28 +15439,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06241014907093464</v>
+        <v>0.06009045093919332</v>
       </c>
       <c r="J2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0124434827179104</v>
+        <v>0.01160513123029461</v>
       </c>
       <c r="M2" t="n">
-        <v>3.111189615797007</v>
+        <v>3.111517345443421</v>
       </c>
       <c r="N2" t="n">
-        <v>16.21440840115396</v>
+        <v>16.20130194370382</v>
       </c>
       <c r="O2" t="n">
-        <v>4.026711859713078</v>
+        <v>4.025084091507136</v>
       </c>
       <c r="P2" t="n">
-        <v>376.9458075713582</v>
+        <v>376.9699143169516</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15475,28 +15521,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08316954179969679</v>
+        <v>0.08115529486324949</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02358373839353223</v>
+        <v>0.02260376511237505</v>
       </c>
       <c r="M3" t="n">
-        <v>3.073606677604394</v>
+        <v>3.074667068200503</v>
       </c>
       <c r="N3" t="n">
-        <v>15.02178805062919</v>
+        <v>15.00313992159314</v>
       </c>
       <c r="O3" t="n">
-        <v>3.875795150756705</v>
+        <v>3.873388687130836</v>
       </c>
       <c r="P3" t="n">
-        <v>391.5455524774653</v>
+        <v>391.5664849159558</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15557,28 +15603,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1152117437126586</v>
+        <v>0.1127807120359002</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04977965579571664</v>
+        <v>0.04799946736741989</v>
       </c>
       <c r="M4" t="n">
-        <v>2.977645253855155</v>
+        <v>2.978667062335207</v>
       </c>
       <c r="N4" t="n">
-        <v>13.29035531037962</v>
+        <v>13.29012301942166</v>
       </c>
       <c r="O4" t="n">
-        <v>3.645593958517544</v>
+        <v>3.645562099240893</v>
       </c>
       <c r="P4" t="n">
-        <v>391.5532980400049</v>
+        <v>391.5785617850411</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15639,28 +15685,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05251955485940223</v>
+        <v>0.05000339929187853</v>
       </c>
       <c r="J5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01251230360575062</v>
+        <v>0.01139584123049786</v>
       </c>
       <c r="M5" t="n">
-        <v>2.662219756186806</v>
+        <v>2.66648210993901</v>
       </c>
       <c r="N5" t="n">
-        <v>11.41844987341426</v>
+        <v>11.42703782806027</v>
       </c>
       <c r="O5" t="n">
-        <v>3.379119689122339</v>
+        <v>3.380390188729737</v>
       </c>
       <c r="P5" t="n">
-        <v>398.2334785674304</v>
+        <v>398.2596269361815</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -15721,28 +15767,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1054601381226312</v>
+        <v>0.1012863583930332</v>
       </c>
       <c r="J6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K6" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03608111649702317</v>
+        <v>0.03336404537284743</v>
       </c>
       <c r="M6" t="n">
-        <v>2.893737741128188</v>
+        <v>2.906857447943144</v>
       </c>
       <c r="N6" t="n">
-        <v>15.5850374185011</v>
+        <v>15.65830395656316</v>
       </c>
       <c r="O6" t="n">
-        <v>3.947788927805171</v>
+        <v>3.957057487144097</v>
       </c>
       <c r="P6" t="n">
-        <v>397.5029630099688</v>
+        <v>397.5463377252938</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -15803,28 +15849,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0507698241966479</v>
+        <v>0.04621722068586238</v>
       </c>
       <c r="J7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01145001806089352</v>
+        <v>0.009461012507510191</v>
       </c>
       <c r="M7" t="n">
-        <v>2.61056982713424</v>
+        <v>2.623223788239362</v>
       </c>
       <c r="N7" t="n">
-        <v>11.67278367886414</v>
+        <v>11.78148870813716</v>
       </c>
       <c r="O7" t="n">
-        <v>3.416545576875002</v>
+        <v>3.432417327210834</v>
       </c>
       <c r="P7" t="n">
-        <v>404.7310388907383</v>
+        <v>404.7783504150786</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15885,28 +15931,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1007066151150208</v>
+        <v>0.09486036399840128</v>
       </c>
       <c r="J8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K8" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05673543692669092</v>
+        <v>0.04974191951213669</v>
       </c>
       <c r="M8" t="n">
-        <v>2.30358282302968</v>
+        <v>2.324721403245154</v>
       </c>
       <c r="N8" t="n">
-        <v>8.844346941715338</v>
+        <v>9.056224249747919</v>
       </c>
       <c r="O8" t="n">
-        <v>2.973944676976244</v>
+        <v>3.009356118798159</v>
       </c>
       <c r="P8" t="n">
-        <v>406.9167195496321</v>
+        <v>406.9774749067258</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15967,28 +16013,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0008677973353375327</v>
+        <v>-0.002808274231148563</v>
       </c>
       <c r="J9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L9" t="n">
-        <v>4.333769389908149e-06</v>
+        <v>4.5251947934144e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.417599547902963</v>
+        <v>2.428722787169669</v>
       </c>
       <c r="N9" t="n">
-        <v>9.114641718158529</v>
+        <v>9.18080284956655</v>
       </c>
       <c r="O9" t="n">
-        <v>3.019046491553008</v>
+        <v>3.029983968532928</v>
       </c>
       <c r="P9" t="n">
-        <v>400.8259756622164</v>
+        <v>400.8641780993456</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16030,7 +16076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J319"/>
+  <dimension ref="A1:J320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32621,6 +32667,58 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-35.434343156299036,174.36204146648447</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-35.43498163661794,174.36230695892172</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-35.43557250612648,174.36272073527675</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-35.436143745738185,174.3632071172809</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-35.43665275984335,174.36377169766808</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-35.43706358723264,174.36443790498075</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-35.43735849922777,174.36513225629065</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-35.43752305278665,174.36593881506423</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J320"/>
+  <dimension ref="A1:J321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11964,6 +11964,42 @@
       <c r="J320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>377.74</v>
+      </c>
+      <c r="C321" t="n">
+        <v>393.53</v>
+      </c>
+      <c r="D321" t="n">
+        <v>392.94</v>
+      </c>
+      <c r="E321" t="n">
+        <v>398.11</v>
+      </c>
+      <c r="F321" t="n">
+        <v>399.83</v>
+      </c>
+      <c r="G321" t="n">
+        <v>402.25</v>
+      </c>
+      <c r="H321" t="n">
+        <v>401.56</v>
+      </c>
+      <c r="I321" t="n">
+        <v>396.75</v>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11978,7 +12014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15271,6 +15307,16 @@
       </c>
       <c r="B329" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -15439,28 +15485,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06009045093919332</v>
+        <v>0.05954553764848065</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01160513123029461</v>
+        <v>0.01148236899902411</v>
       </c>
       <c r="M2" t="n">
-        <v>3.111517345443421</v>
+        <v>3.104117339325136</v>
       </c>
       <c r="N2" t="n">
-        <v>16.20130194370382</v>
+        <v>16.15273573332402</v>
       </c>
       <c r="O2" t="n">
-        <v>4.025084091507136</v>
+        <v>4.019046619949068</v>
       </c>
       <c r="P2" t="n">
-        <v>376.9699143169516</v>
+        <v>376.9756119063567</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15521,28 +15567,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08115529486324949</v>
+        <v>0.08103104914197147</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02260376511237505</v>
+        <v>0.02270376570307708</v>
       </c>
       <c r="M3" t="n">
-        <v>3.074667068200503</v>
+        <v>3.065707792917549</v>
       </c>
       <c r="N3" t="n">
-        <v>15.00313992159314</v>
+        <v>14.95636235443763</v>
       </c>
       <c r="O3" t="n">
-        <v>3.873388687130836</v>
+        <v>3.867345647138051</v>
       </c>
       <c r="P3" t="n">
-        <v>391.5664849159558</v>
+        <v>391.5677840237537</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15603,28 +15649,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1127807120359002</v>
+        <v>0.1116999380022087</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04799946736741989</v>
+        <v>0.04744131264480145</v>
       </c>
       <c r="M4" t="n">
-        <v>2.978667062335207</v>
+        <v>2.973880780339276</v>
       </c>
       <c r="N4" t="n">
-        <v>13.29012301942166</v>
+        <v>13.25670630749537</v>
       </c>
       <c r="O4" t="n">
-        <v>3.645562099240893</v>
+        <v>3.640976010288363</v>
       </c>
       <c r="P4" t="n">
-        <v>391.5785617850411</v>
+        <v>391.5898623108102</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15685,28 +15731,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05000339929187853</v>
+        <v>0.04902423047287696</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01139584123049786</v>
+        <v>0.0110349155703362</v>
       </c>
       <c r="M5" t="n">
-        <v>2.66648210993901</v>
+        <v>2.662972117682151</v>
       </c>
       <c r="N5" t="n">
-        <v>11.42703782806027</v>
+        <v>11.39798918592064</v>
       </c>
       <c r="O5" t="n">
-        <v>3.380390188729737</v>
+        <v>3.376090814228883</v>
       </c>
       <c r="P5" t="n">
-        <v>398.2596269361815</v>
+        <v>398.269865082294</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -15767,28 +15813,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1012863583930332</v>
+        <v>0.1010210107244407</v>
       </c>
       <c r="J6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03336404537284743</v>
+        <v>0.0334386351382987</v>
       </c>
       <c r="M6" t="n">
-        <v>2.906857447943144</v>
+        <v>2.899169168582711</v>
       </c>
       <c r="N6" t="n">
-        <v>15.65830395656316</v>
+        <v>15.60986091015402</v>
       </c>
       <c r="O6" t="n">
-        <v>3.957057487144097</v>
+        <v>3.950931650908937</v>
       </c>
       <c r="P6" t="n">
-        <v>397.5463377252938</v>
+        <v>397.5491121888479</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -15849,28 +15895,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04621722068586238</v>
+        <v>0.04371381085969678</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009461012507510191</v>
+        <v>0.008505007557232713</v>
       </c>
       <c r="M7" t="n">
-        <v>2.623223788239362</v>
+        <v>2.626540401983478</v>
       </c>
       <c r="N7" t="n">
-        <v>11.78148870813716</v>
+        <v>11.78821055876233</v>
       </c>
       <c r="O7" t="n">
-        <v>3.432417327210834</v>
+        <v>3.433396359111824</v>
       </c>
       <c r="P7" t="n">
-        <v>404.7783504150786</v>
+        <v>404.8045259581335</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15931,28 +15977,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09486036399840128</v>
+        <v>0.08957509222671707</v>
       </c>
       <c r="J8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04974191951213669</v>
+        <v>0.04401451600488893</v>
       </c>
       <c r="M8" t="n">
-        <v>2.324721403245154</v>
+        <v>2.34366555019326</v>
       </c>
       <c r="N8" t="n">
-        <v>9.056224249747919</v>
+        <v>9.221989444620728</v>
       </c>
       <c r="O8" t="n">
-        <v>3.009356118798159</v>
+        <v>3.036772866814495</v>
       </c>
       <c r="P8" t="n">
-        <v>406.9774749067258</v>
+        <v>407.0327374759506</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16013,28 +16059,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.002808274231148563</v>
+        <v>-0.005504146154118946</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L9" t="n">
-        <v>4.5251947934144e-05</v>
+        <v>0.0001741759822306843</v>
       </c>
       <c r="M9" t="n">
-        <v>2.428722787169669</v>
+        <v>2.434927766421478</v>
       </c>
       <c r="N9" t="n">
-        <v>9.18080284956655</v>
+        <v>9.202603737453638</v>
       </c>
       <c r="O9" t="n">
-        <v>3.029983968532928</v>
+        <v>3.03357936066516</v>
       </c>
       <c r="P9" t="n">
-        <v>400.8641780993456</v>
+        <v>400.892366017621</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16076,7 +16122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J320"/>
+  <dimension ref="A1:J321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32719,6 +32765,58 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-35.434339967037516,174.36207028423885</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-35.434973394753534,174.36233646063863</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-35.435563255949646,174.3627397738503</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-35.436131151213964,174.36322696535603</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-35.43661452117075,174.36381575606026</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-35.43704101161631,174.36445669560567</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-35.43735176010777,174.36513507090012</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-35.43751034613903,174.36594147353242</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J321"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12000,6 +12000,42 @@
       <c r="J321" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="C322" t="n">
+        <v>394.07</v>
+      </c>
+      <c r="D322" t="n">
+        <v>391.39</v>
+      </c>
+      <c r="E322" t="n">
+        <v>396.91</v>
+      </c>
+      <c r="F322" t="n">
+        <v>400.35</v>
+      </c>
+      <c r="G322" t="n">
+        <v>403.32</v>
+      </c>
+      <c r="H322" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="I322" t="n">
+        <v>395.89</v>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B330"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15317,6 +15353,16 @@
       </c>
       <c r="B330" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -15485,28 +15531,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05954553764848065</v>
+        <v>0.05770882361825576</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01148236899902411</v>
+        <v>0.01085859998799443</v>
       </c>
       <c r="M2" t="n">
-        <v>3.104117339325136</v>
+        <v>3.102283017273066</v>
       </c>
       <c r="N2" t="n">
-        <v>16.15273573332402</v>
+        <v>16.12583022685453</v>
       </c>
       <c r="O2" t="n">
-        <v>4.019046619949068</v>
+        <v>4.015697975054216</v>
       </c>
       <c r="P2" t="n">
-        <v>376.9756119063567</v>
+        <v>376.9948991200039</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15567,28 +15613,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08103104914197147</v>
+        <v>0.08126637544438668</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02270376570307708</v>
+        <v>0.02300307798056411</v>
       </c>
       <c r="M3" t="n">
-        <v>3.065707792917549</v>
+        <v>3.057120044375409</v>
       </c>
       <c r="N3" t="n">
-        <v>14.95636235443763</v>
+        <v>14.91015369002881</v>
       </c>
       <c r="O3" t="n">
-        <v>3.867345647138051</v>
+        <v>3.861366816300779</v>
       </c>
       <c r="P3" t="n">
-        <v>391.5677840237537</v>
+        <v>391.5653128776761</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15649,28 +15695,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1116999380022087</v>
+        <v>0.1095919569556895</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04744131264480145</v>
+        <v>0.04598060957400429</v>
       </c>
       <c r="M4" t="n">
-        <v>2.973880780339276</v>
+        <v>2.973316107650439</v>
       </c>
       <c r="N4" t="n">
-        <v>13.25670630749537</v>
+        <v>13.24624969262291</v>
       </c>
       <c r="O4" t="n">
-        <v>3.640976010288363</v>
+        <v>3.639539763846922</v>
       </c>
       <c r="P4" t="n">
-        <v>391.5898623108102</v>
+        <v>391.6119980816157</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15731,28 +15777,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04902423047287696</v>
+        <v>0.04724974216990731</v>
       </c>
       <c r="J5" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K5" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0110349155703362</v>
+        <v>0.01031669304300997</v>
       </c>
       <c r="M5" t="n">
-        <v>2.662972117682151</v>
+        <v>2.663314330973693</v>
       </c>
       <c r="N5" t="n">
-        <v>11.39798918592064</v>
+        <v>11.38433633388814</v>
       </c>
       <c r="O5" t="n">
-        <v>3.376090814228883</v>
+        <v>3.374068217136124</v>
       </c>
       <c r="P5" t="n">
-        <v>398.269865082294</v>
+        <v>398.2884988676576</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -15813,28 +15859,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1010210107244407</v>
+        <v>0.1010981960072562</v>
       </c>
       <c r="J6" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K6" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0334386351382987</v>
+        <v>0.03373577377981773</v>
       </c>
       <c r="M6" t="n">
-        <v>2.899169168582711</v>
+        <v>2.890450687106394</v>
       </c>
       <c r="N6" t="n">
-        <v>15.60986091015402</v>
+        <v>15.56127340959302</v>
       </c>
       <c r="O6" t="n">
-        <v>3.950931650908937</v>
+        <v>3.944777992434177</v>
       </c>
       <c r="P6" t="n">
-        <v>397.5491121888479</v>
+        <v>397.548301671252</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -15895,28 +15941,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04371381085969678</v>
+        <v>0.04195019135853253</v>
       </c>
       <c r="J7" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K7" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008505007557232713</v>
+        <v>0.007883043876360851</v>
       </c>
       <c r="M7" t="n">
-        <v>2.626540401983478</v>
+        <v>2.626444051839204</v>
       </c>
       <c r="N7" t="n">
-        <v>11.78821055876233</v>
+        <v>11.77307515967707</v>
       </c>
       <c r="O7" t="n">
-        <v>3.433396359111824</v>
+        <v>3.431191507286801</v>
       </c>
       <c r="P7" t="n">
-        <v>404.8045259581335</v>
+        <v>404.8230456109217</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -15977,28 +16023,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08957509222671707</v>
+        <v>0.08313982051922521</v>
       </c>
       <c r="J8" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K8" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04401451600488893</v>
+        <v>0.03730936927459738</v>
       </c>
       <c r="M8" t="n">
-        <v>2.34366555019326</v>
+        <v>2.368760612322309</v>
       </c>
       <c r="N8" t="n">
-        <v>9.221989444620728</v>
+        <v>9.480693332839875</v>
       </c>
       <c r="O8" t="n">
-        <v>3.036772866814495</v>
+        <v>3.079073453628522</v>
       </c>
       <c r="P8" t="n">
-        <v>407.0327374759506</v>
+        <v>407.1003138423619</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16059,28 +16105,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.005504146154118946</v>
+        <v>-0.00874240192653721</v>
       </c>
       <c r="J9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K9" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001741759822306843</v>
+        <v>0.0004391736542559421</v>
       </c>
       <c r="M9" t="n">
-        <v>2.434927766421478</v>
+        <v>2.443762010178126</v>
       </c>
       <c r="N9" t="n">
-        <v>9.202603737453638</v>
+        <v>9.246717341065326</v>
       </c>
       <c r="O9" t="n">
-        <v>3.03357936066516</v>
+        <v>3.040841551456657</v>
       </c>
       <c r="P9" t="n">
-        <v>400.892366017621</v>
+        <v>400.9263707292413</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16122,7 +16168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J321"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32817,6 +32863,58 @@
         </is>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-35.434342310662174,174.36204910755595</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-35.43497182210015,174.36234208994082</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-35.435570389170856,174.36272509236363</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-35.43613777991131,174.36321651900147</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-35.43661111051653,174.36381968579477</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-35.43703303936829,174.3644633312364</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-35.43736720036998,174.36512862223728</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-35.43751798789914,174.36593987473347</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J322"/>
+  <dimension ref="A1:J324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12034,6 +12034,78 @@
         <v>395.89</v>
       </c>
       <c r="J322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="C323" t="n">
+        <v>389.45</v>
+      </c>
+      <c r="D323" t="n">
+        <v>389.93</v>
+      </c>
+      <c r="E323" t="n">
+        <v>394.96</v>
+      </c>
+      <c r="F323" t="n">
+        <v>399.21</v>
+      </c>
+      <c r="G323" t="n">
+        <v>401.76</v>
+      </c>
+      <c r="H323" t="n">
+        <v>398.86</v>
+      </c>
+      <c r="I323" t="n">
+        <v>394.78</v>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="C324" t="n">
+        <v>388.67</v>
+      </c>
+      <c r="D324" t="n">
+        <v>388.83</v>
+      </c>
+      <c r="E324" t="n">
+        <v>394.22</v>
+      </c>
+      <c r="F324" t="n">
+        <v>400.11</v>
+      </c>
+      <c r="G324" t="n">
+        <v>402.01</v>
+      </c>
+      <c r="H324" t="n">
+        <v>398.63</v>
+      </c>
+      <c r="I324" t="n">
+        <v>394.86</v>
+      </c>
+      <c r="J324" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12050,7 +12122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B331"/>
+  <dimension ref="A1:B333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15363,6 +15435,26 @@
       </c>
       <c r="B331" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -15531,28 +15623,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05770882361825576</v>
+        <v>0.05021781507380996</v>
       </c>
       <c r="J2" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01085859998799443</v>
+        <v>0.008267570768557886</v>
       </c>
       <c r="M2" t="n">
-        <v>3.102283017273066</v>
+        <v>3.115046184861298</v>
       </c>
       <c r="N2" t="n">
-        <v>16.12583022685453</v>
+        <v>16.2243220357689</v>
       </c>
       <c r="O2" t="n">
-        <v>4.015697975054216</v>
+        <v>4.027942655471761</v>
       </c>
       <c r="P2" t="n">
-        <v>376.9948991200039</v>
+        <v>377.0737988562334</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15613,28 +15705,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08126637544438668</v>
+        <v>0.07513792832381376</v>
       </c>
       <c r="J3" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02300307798056411</v>
+        <v>0.01985100019983987</v>
       </c>
       <c r="M3" t="n">
-        <v>3.057120044375409</v>
+        <v>3.070567412545904</v>
       </c>
       <c r="N3" t="n">
-        <v>14.91015369002881</v>
+        <v>14.95073276890357</v>
       </c>
       <c r="O3" t="n">
-        <v>3.861366816300779</v>
+        <v>3.866617742795837</v>
       </c>
       <c r="P3" t="n">
-        <v>391.5653128776761</v>
+        <v>391.6298615073906</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15695,28 +15787,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1095919569556895</v>
+        <v>0.1028235356044369</v>
       </c>
       <c r="J4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04598060957400429</v>
+        <v>0.04081210543655323</v>
       </c>
       <c r="M4" t="n">
-        <v>2.973316107650439</v>
+        <v>2.9827777433861</v>
       </c>
       <c r="N4" t="n">
-        <v>13.24624969262291</v>
+        <v>13.32705203856641</v>
       </c>
       <c r="O4" t="n">
-        <v>3.639539763846922</v>
+        <v>3.650623513670837</v>
       </c>
       <c r="P4" t="n">
-        <v>391.6119980816157</v>
+        <v>391.6832880250032</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15777,28 +15869,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04724974216990731</v>
+        <v>0.04073751746614542</v>
       </c>
       <c r="J5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K5" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01031669304300997</v>
+        <v>0.007704425651468783</v>
       </c>
       <c r="M5" t="n">
-        <v>2.663314330973693</v>
+        <v>2.678291971870207</v>
       </c>
       <c r="N5" t="n">
-        <v>11.38433633388814</v>
+        <v>11.46368498615359</v>
       </c>
       <c r="O5" t="n">
-        <v>3.374068217136124</v>
+        <v>3.385806401162593</v>
       </c>
       <c r="P5" t="n">
-        <v>398.2884988676576</v>
+        <v>398.3570893987684</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -15859,28 +15951,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1010981960072562</v>
+        <v>0.1003383420368796</v>
       </c>
       <c r="J6" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K6" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03373577377981773</v>
+        <v>0.03373076617682558</v>
       </c>
       <c r="M6" t="n">
-        <v>2.890450687106394</v>
+        <v>2.876525715608263</v>
       </c>
       <c r="N6" t="n">
-        <v>15.56127340959302</v>
+        <v>15.46821233502005</v>
       </c>
       <c r="O6" t="n">
-        <v>3.944777992434177</v>
+        <v>3.932964827584917</v>
       </c>
       <c r="P6" t="n">
-        <v>397.548301671252</v>
+        <v>397.5563019471693</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -15941,28 +16033,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04195019135853253</v>
+        <v>0.03662811206158532</v>
       </c>
       <c r="J7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K7" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007883043876360851</v>
+        <v>0.006061055448861929</v>
       </c>
       <c r="M7" t="n">
-        <v>2.626444051839204</v>
+        <v>2.634779331617162</v>
       </c>
       <c r="N7" t="n">
-        <v>11.77307515967707</v>
+        <v>11.79980572467065</v>
       </c>
       <c r="O7" t="n">
-        <v>3.431191507286801</v>
+        <v>3.435084529479682</v>
       </c>
       <c r="P7" t="n">
-        <v>404.8230456109217</v>
+        <v>404.8790983054589</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16023,28 +16115,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08313982051922521</v>
+        <v>0.06926130696441057</v>
       </c>
       <c r="J8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K8" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03730936927459738</v>
+        <v>0.02484374960763724</v>
       </c>
       <c r="M8" t="n">
-        <v>2.368760612322309</v>
+        <v>2.426271584601747</v>
       </c>
       <c r="N8" t="n">
-        <v>9.480693332839875</v>
+        <v>10.09886969173153</v>
       </c>
       <c r="O8" t="n">
-        <v>3.079073453628522</v>
+        <v>3.177871880949817</v>
       </c>
       <c r="P8" t="n">
-        <v>407.1003138423619</v>
+        <v>407.2464863993195</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16105,28 +16197,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.00874240192653721</v>
+        <v>-0.01645325364350989</v>
       </c>
       <c r="J9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K9" t="n">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0004391736542559421</v>
+        <v>0.001542459185752243</v>
       </c>
       <c r="M9" t="n">
-        <v>2.443762010178126</v>
+        <v>2.467634815161644</v>
       </c>
       <c r="N9" t="n">
-        <v>9.246717341065326</v>
+        <v>9.398398251331894</v>
       </c>
       <c r="O9" t="n">
-        <v>3.040841551456657</v>
+        <v>3.065680715816945</v>
       </c>
       <c r="P9" t="n">
-        <v>400.9263707292413</v>
+        <v>401.0075830585205</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16168,7 +16260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J322"/>
+  <dimension ref="A1:J324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32915,6 +33007,110 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-35.43434536703311,174.36202149053963</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-35.43498527701515,174.36229392812606</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-35.43557710820342,174.36271126334793</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-35.436148551542644,174.3631995436716</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-35.43661858771985,174.36381107060714</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-35.43704466245873,174.36445365685844</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-35.43737479254298,174.36512545134693</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-35.43752785110114,174.36593781116696</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.434346430117195,174.3620118846204</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.4349875486223,174.36228579690894</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-35.43558217048723,174.362700844225</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-35.43615263923803,174.3631931017504</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-35.43661268466465,174.3638178720712</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-35.43704279978403,174.3644552072397</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-35.437376754565214,174.36512463190326</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-35.43752714023972,174.36593795989248</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J324"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12106,6 +12106,78 @@
         <v>394.86</v>
       </c>
       <c r="J324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>373.75</v>
+      </c>
+      <c r="C325" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="D325" t="n">
+        <v>390.28</v>
+      </c>
+      <c r="E325" t="n">
+        <v>395.35</v>
+      </c>
+      <c r="F325" t="n">
+        <v>399.76</v>
+      </c>
+      <c r="G325" t="n">
+        <v>403.48</v>
+      </c>
+      <c r="H325" t="n">
+        <v>400.07</v>
+      </c>
+      <c r="I325" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="C326" t="n">
+        <v>389.79</v>
+      </c>
+      <c r="D326" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="E326" t="n">
+        <v>396.37</v>
+      </c>
+      <c r="F326" t="n">
+        <v>400.23</v>
+      </c>
+      <c r="G326" t="n">
+        <v>403.2</v>
+      </c>
+      <c r="H326" t="n">
+        <v>400.02</v>
+      </c>
+      <c r="I326" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="J326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12122,7 +12194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B333"/>
+  <dimension ref="A1:B335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15455,6 +15527,26 @@
       </c>
       <c r="B333" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -15623,28 +15715,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05021781507380996</v>
+        <v>0.04366799800032466</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008267570768557886</v>
+        <v>0.006297951139159097</v>
       </c>
       <c r="M2" t="n">
-        <v>3.115046184861298</v>
+        <v>3.12426425275424</v>
       </c>
       <c r="N2" t="n">
-        <v>16.2243220357689</v>
+        <v>16.2793323541907</v>
       </c>
       <c r="O2" t="n">
-        <v>4.027942655471761</v>
+        <v>4.034765464582879</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0737988562334</v>
+        <v>377.1430214242816</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15705,28 +15797,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07513792832381376</v>
+        <v>0.06981017878291991</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01985100019983987</v>
+        <v>0.01731974486432697</v>
       </c>
       <c r="M3" t="n">
-        <v>3.070567412545904</v>
+        <v>3.079891666396759</v>
       </c>
       <c r="N3" t="n">
-        <v>14.95073276890357</v>
+        <v>14.96102567002999</v>
       </c>
       <c r="O3" t="n">
-        <v>3.866617742795837</v>
+        <v>3.867948509226821</v>
       </c>
       <c r="P3" t="n">
-        <v>391.6298615073906</v>
+        <v>391.6861650627098</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15787,28 +15879,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1028235356044369</v>
+        <v>0.09768642068726117</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04081210543655323</v>
+        <v>0.03726276863326072</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9827777433861</v>
+        <v>2.985796108127109</v>
       </c>
       <c r="N4" t="n">
-        <v>13.32705203856641</v>
+        <v>13.3399490007235</v>
       </c>
       <c r="O4" t="n">
-        <v>3.650623513670837</v>
+        <v>3.65238949192491</v>
       </c>
       <c r="P4" t="n">
-        <v>391.6832880250032</v>
+        <v>391.7375773855173</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15869,28 +15961,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04073751746614542</v>
+        <v>0.03609324207700023</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007704425651468783</v>
+        <v>0.00610659487335008</v>
       </c>
       <c r="M5" t="n">
-        <v>2.678291971870207</v>
+        <v>2.684245465844433</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46368498615359</v>
+        <v>11.47217112860363</v>
       </c>
       <c r="O5" t="n">
-        <v>3.385806401162593</v>
+        <v>3.387059363017369</v>
       </c>
       <c r="P5" t="n">
-        <v>398.3570893987684</v>
+        <v>398.4061683469965</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -15951,28 +16043,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1003383420368796</v>
+        <v>0.1000207574177241</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03373076617682558</v>
+        <v>0.03401153389102041</v>
       </c>
       <c r="M6" t="n">
-        <v>2.876525715608263</v>
+        <v>2.860461562491124</v>
       </c>
       <c r="N6" t="n">
-        <v>15.46821233502005</v>
+        <v>15.37372570182128</v>
       </c>
       <c r="O6" t="n">
-        <v>3.932964827584917</v>
+        <v>3.920934289403647</v>
       </c>
       <c r="P6" t="n">
-        <v>397.5563019471693</v>
+        <v>397.5596568785789</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16033,28 +16125,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03662811206158532</v>
+        <v>0.03336506779362781</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006061055448861929</v>
+        <v>0.005093406696889735</v>
       </c>
       <c r="M7" t="n">
-        <v>2.634779331617162</v>
+        <v>2.633720222176228</v>
       </c>
       <c r="N7" t="n">
-        <v>11.79980572467065</v>
+        <v>11.76551942283234</v>
       </c>
       <c r="O7" t="n">
-        <v>3.435084529479682</v>
+        <v>3.430090293685042</v>
       </c>
       <c r="P7" t="n">
-        <v>404.8790983054589</v>
+        <v>404.9135838958882</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16115,28 +16207,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06926130696441057</v>
+        <v>0.05752748964197369</v>
       </c>
       <c r="J8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02484374960763724</v>
+        <v>0.01671941149755041</v>
       </c>
       <c r="M8" t="n">
-        <v>2.426271584601747</v>
+        <v>2.474424476757823</v>
       </c>
       <c r="N8" t="n">
-        <v>10.09886969173153</v>
+        <v>10.53077788020263</v>
       </c>
       <c r="O8" t="n">
-        <v>3.177871880949817</v>
+        <v>3.24511600412106</v>
       </c>
       <c r="P8" t="n">
-        <v>407.2464863993195</v>
+        <v>407.3704927533396</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16197,28 +16289,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01645325364350989</v>
+        <v>-0.02555158343216537</v>
       </c>
       <c r="J9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001542459185752243</v>
+        <v>0.003651999532261141</v>
       </c>
       <c r="M9" t="n">
-        <v>2.467634815161644</v>
+        <v>2.49929094831499</v>
       </c>
       <c r="N9" t="n">
-        <v>9.398398251331894</v>
+        <v>9.637604615299439</v>
       </c>
       <c r="O9" t="n">
-        <v>3.065680715816945</v>
+        <v>3.104449164553905</v>
       </c>
       <c r="P9" t="n">
-        <v>401.0075830585205</v>
+        <v>401.1037367013911</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16260,7 +16352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J324"/>
+  <dimension ref="A1:J326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33111,6 +33203,110 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.43434478716876,174.36202673013187</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.434985830355394,174.362291947445</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.435575497476584,174.36271457852314</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.43614639721657,174.36320293873797</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-35.43661498029727,174.36381522705753</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-35.4370318472564,174.36446432348015</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-35.43736447059988,174.36512976233254</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-35.437538780595176,174.3659355245116</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-35.434345729448225,174.36201821579448</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-35.43498428682724,174.36229747250258</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-35.4355737947081,174.36271808313677</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-35.43614076282484,174.36321181814134</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-35.436611897590595,174.363818778933</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-35.4370339334522,174.3644625870536</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>-35.43736489712646,174.36512958419266</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-35.437538780595176,174.3659355245116</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
